--- a/AAII_Financials/Quarterly/VNT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VNT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="92">
   <si>
     <t>VNT</t>
   </si>
@@ -656,426 +656,438 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46206</v>
+      </c>
+      <c r="E7" s="2">
         <v>46115</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45835</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45744</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45562</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45471</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45380</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45198</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44743</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44652</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44470</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44379</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44288</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44099</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43917</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43735</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43644</v>
       </c>
-      <c r="AE7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AG7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>756700</v>
+      </c>
+      <c r="E8" s="3">
         <v>750600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>808500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>752500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>773500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>741100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>776800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>750000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>696400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>755800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>789000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>765400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>764400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>776400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>871900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>788000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>776400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>748100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>790200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>768500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>724600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>707400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>815000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>746700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>533700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>609200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>714400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1314400</v>
       </c>
-      <c r="AE8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>391700</v>
+      </c>
+      <c r="E9" s="3">
         <v>398300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>432600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>396400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>403100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>390900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>412600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>395800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>360900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>383800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>407700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>406400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>416300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>423400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>486900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>428100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>428300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>412800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>433800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>422100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>406100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>395600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>452300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>415400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>302700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>346100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>406400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>757200</v>
       </c>
-      <c r="AE9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>365000</v>
+      </c>
+      <c r="E10" s="3">
         <v>352300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>375900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>356100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>370400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>350200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>364200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>354200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>335500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>372000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>381300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>359000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>348100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>353000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>385000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>359900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>348100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>335300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>356400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>346400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>318500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>311800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>362700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>331300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>231000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>263100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>308000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>557200</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1109,103 +1121,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>35100</v>
+      </c>
+      <c r="E12" s="3">
         <v>41400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>43600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>44400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>47500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>40200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>42400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>45700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>45100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>44500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>43100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>39100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>40300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>41000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>40200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>35000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>34900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>34500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>32000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>31200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>32900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>33200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>32500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>31600</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>29200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>32900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>34800</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>67200</v>
       </c>
-      <c r="AE12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1299,76 +1315,79 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>86200</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>3300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-3400</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>6600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>13500</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>2600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-35100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>25200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-34100</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
         <v>200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-3200</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1377,16 +1396,16 @@
         <v>0</v>
       </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>85300</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-      <c r="AE14" s="3" t="s">
-        <v>3</v>
+      <c r="AE14" s="3">
+        <v>0</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>3</v>
@@ -1394,31 +1413,34 @@
       <c r="AG14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E15" s="3">
         <v>17100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>17000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>18300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>19200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>19600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>19700</v>
-      </c>
-      <c r="J15" s="3">
-        <v>20000</v>
       </c>
       <c r="K15" s="3">
         <v>20000</v>
@@ -1427,28 +1449,28 @@
         <v>20000</v>
       </c>
       <c r="M15" s="3">
-        <v>20100</v>
+        <v>20000</v>
       </c>
       <c r="N15" s="3">
         <v>20100</v>
       </c>
       <c r="O15" s="3">
+        <v>20100</v>
+      </c>
+      <c r="P15" s="3">
         <v>20300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>20700</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T15" s="3">
-        <v>0</v>
+      <c r="T15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U15" s="3">
         <v>0</v>
@@ -1489,8 +1511,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1521,198 +1546,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>610000</v>
+      </c>
+      <c r="E17" s="3">
         <v>615800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>652400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>610100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>637100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>604400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>614000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>618500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>582300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>609000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>617400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>622800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>643800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>642600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>715500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>637800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>639900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>613300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>629200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>597900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>603600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>574500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>637200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>568100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>443700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>587400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>559500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1069000</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>146700</v>
+      </c>
+      <c r="E18" s="3">
         <v>134800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>156100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>142400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>136400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>136700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>162800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>131500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>114100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>146800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>171600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>142600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>120600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>133800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>156400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>150200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>136500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>134800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>161000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>170600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>121000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>132900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>177800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>178600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>90000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>21800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>154900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>245400</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1746,245 +1778,252 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3">
         <v>-1900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3900</v>
-      </c>
-      <c r="I20" s="3">
-        <v>300</v>
       </c>
       <c r="J20" s="3">
         <v>300</v>
       </c>
       <c r="K20" s="3">
+        <v>300</v>
+      </c>
+      <c r="L20" s="3">
         <v>1100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-55600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-82300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-95300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>182700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-13400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-12200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-11900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-10600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-6700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1800</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>162200</v>
+      </c>
+      <c r="E21" s="3">
         <v>151900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>175000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>165700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>155500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>152400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>182200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>151200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>133000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>166600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>192700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>162500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>140400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>153600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>132900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>96600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>70200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>346600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>176900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>178400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>128300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>142100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>189800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>199000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>109200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>40600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>178800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>288500</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E22" s="3">
         <v>13700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>14300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>14800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>15600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>15100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>18500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>18900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>18400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>18900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>23000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>22800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>23900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>24000</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="R22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1999,31 +2038,31 @@
         <v>0</v>
       </c>
       <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
         <v>200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>3200</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA22" s="3">
-        <v>0</v>
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>3</v>
+      <c r="AC22" s="3">
+        <v>0</v>
       </c>
       <c r="AD22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE22" s="3">
-        <v>0</v>
+      <c r="AE22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF22" s="3">
         <v>0</v>
@@ -2031,198 +2070,207 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>43800</v>
+      </c>
+      <c r="E23" s="3">
         <v>121100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>140400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>136000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>120700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>111100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>130500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>112300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>92000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>162800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>124400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>119900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>130300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>108900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>100800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>67900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>41200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>317500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>147600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>158400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>108900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>119100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>171100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>178300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>89600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>21300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>157600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>247200</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E24" s="3">
         <v>26800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>16900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>33200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>28800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>23200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>20500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>21900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>26000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>18200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>29300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>33000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>26100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>33100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>17800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>67300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>35200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>31100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>26600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>28100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>34300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>37300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>21200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>25500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>36600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>57900</v>
       </c>
-      <c r="AE24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2316,198 +2364,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E26" s="3">
         <v>94300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>123500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>102800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>91900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>87900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>123500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>91800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>70100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>136800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>106200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>90600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>97300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>82800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>67700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>50100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>33300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>250200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>112400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>127300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>82300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>91000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>136800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>141000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>68400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>121000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>189300</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E27" s="3">
         <v>94300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>123500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>102800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>91900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>87900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>123500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>91800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>70100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>136800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>106200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>90600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>97300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>82800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>67700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>50100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>33300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>250200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>112400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>127300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>82300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>91000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>136800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>141000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>68400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>121000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>189300</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2601,8 +2658,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2696,8 +2756,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2791,8 +2854,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2886,198 +2952,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3">
         <v>1900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3900</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-300</v>
       </c>
       <c r="J32" s="3">
         <v>-300</v>
       </c>
       <c r="K32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L32" s="3">
         <v>-1100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>55600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>82300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>95300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-182700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>13400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>12200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>11900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>10600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>6700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E33" s="3">
         <v>94300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>123500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>102800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>91900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>87900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>123500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>91800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>70100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>136800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>106200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>90600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>97300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>82800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>67700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>50100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>33300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>250200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>112400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>127300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>82300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>91000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>136800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>141000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>68400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>121000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>189300</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3171,203 +3246,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E35" s="3">
         <v>94300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>123500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>102800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>91900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>87900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>123500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>91800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>70100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>136800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>106200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>90600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>97300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>82800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>67700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>50100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>33300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>250200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>112400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>127300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>82300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>91000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>136800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>141000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>68400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>121000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>189300</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46206</v>
+      </c>
+      <c r="E38" s="2">
         <v>46115</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45835</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45744</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45562</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45471</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45380</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45198</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44743</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44652</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44470</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44379</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44288</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44099</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43917</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43735</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43644</v>
       </c>
-      <c r="AE38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AG38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3401,8 +3485,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3436,80 +3521,81 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>265800</v>
+      </c>
+      <c r="E41" s="3">
         <v>233800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>492200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>433800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>364200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>333600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>356400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>330900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>331300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>406000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>340900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>263600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>244000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>208200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>204500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>121700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>127400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>145100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>572600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>458900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>703400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>670300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>380500</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3525,14 +3611,17 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF41" s="3">
-        <v>0</v>
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3576,20 +3665,20 @@
         <v>0</v>
       </c>
       <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>21300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>67100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>135100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>215100</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3605,8 +3694,8 @@
       <c r="Z42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA42" s="3">
-        <v>0</v>
+      <c r="AA42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB42" s="3">
         <v>0</v>
@@ -3626,86 +3715,89 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>576000</v>
+      </c>
+      <c r="E43" s="3">
         <v>540500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>537200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>581200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>541500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>540000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>534100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>539800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>504300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>525600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>504300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>531000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>501600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>484900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>514800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>511200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>482400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>434200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>481300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>473800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>397900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>386500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>447100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>431100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>389700</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3721,86 +3813,89 @@
       <c r="AG43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>323000</v>
+      </c>
+      <c r="E44" s="3">
         <v>341500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>326500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>358800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>368500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>356100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>337800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>333000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>323100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>294800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>296600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>314300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>329200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>350800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>346000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>377500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>326400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>325400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>287000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>263800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>250300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>242700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>233700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>217600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>222900</v>
       </c>
-      <c r="AB44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3816,86 +3911,89 @@
       <c r="AG44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E45" s="3">
         <v>18600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>18000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>18400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>17100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>15400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>14100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>14100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>12300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>68800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>69400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>72500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>164500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>298400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>262500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>274600</v>
-      </c>
-      <c r="T45" s="3">
-        <v>137300</v>
       </c>
       <c r="U45" s="3">
         <v>137300</v>
       </c>
       <c r="V45" s="3">
+        <v>137300</v>
+      </c>
+      <c r="W45" s="3">
         <v>124600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>118100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>111700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>120800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>107600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>103900</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3911,86 +4009,89 @@
       <c r="AG45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1279700</v>
+      </c>
+      <c r="E46" s="3">
         <v>1266700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1491800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1525100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1418000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1369600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1370000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1343000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1292600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1361400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1332500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1303200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1276200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1339500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1385000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1340000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1345900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1257100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1478200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1321100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1469700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1411200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1182100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>756300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>716500</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4006,8 +4107,11 @@
       <c r="AG46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4050,42 +4154,42 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3">
         <v>249800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>249200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>244800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>243300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>300600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>301600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>297700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>293600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>282500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>292500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>295300</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4101,86 +4205,89 @@
       <c r="AG47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>171500</v>
+      </c>
+      <c r="E48" s="3">
         <v>168700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>163900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>154400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>167400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>164900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>167000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>173700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>161600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>155100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>149300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>135700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>136500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>135200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>136600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>134700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>127700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>146100</v>
-      </c>
-      <c r="U48" s="3">
-        <v>146000</v>
       </c>
       <c r="V48" s="3">
         <v>146000</v>
       </c>
       <c r="W48" s="3">
+        <v>146000</v>
+      </c>
+      <c r="X48" s="3">
         <v>133600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>133900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>136900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>134600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>128100</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4196,86 +4303,89 @@
       <c r="AG48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1979800</v>
+      </c>
+      <c r="E49" s="3">
         <v>2152400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2170000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2172200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2220300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2193200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2212500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2252500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2255400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2278500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2310700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2306700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2340500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2365900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2388400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2383200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2350500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2506300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2283100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2296300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1314000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1324000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1342600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1309600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1314300</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4291,8 +4401,11 @@
       <c r="AG49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4386,8 +4499,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4481,86 +4597,89 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>220000</v>
+      </c>
+      <c r="E52" s="3">
         <v>255500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>48800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>247300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>287500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>280100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>46100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>249500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>239100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>232100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>21400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>204300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>187400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>184100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>183500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>156600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>150300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>147300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>141900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>106600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>124700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>121400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>128900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>110700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>111400</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4576,8 +4695,11 @@
       <c r="AG52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4671,86 +4793,89 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4031000</v>
+      </c>
+      <c r="E54" s="3">
         <v>4131300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4368800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4380000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4375800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4293300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4310500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4307100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4235900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4305800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4294000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4221900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4205600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4278500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4343300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4263700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4219200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4300100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4349800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4171600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3339700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3284100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3073000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2603700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2565600</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4766,8 +4891,11 @@
       <c r="AG54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4801,8 +4929,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4836,86 +4965,87 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>356400</v>
+      </c>
+      <c r="E57" s="3">
         <v>366800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>361600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>345700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>342800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>372600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>378100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>370200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>367700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>384900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>366800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>352100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>353900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>373700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>430900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>413500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>387700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>407900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>424900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>390500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>363800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>375100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>367400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>356300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>287700</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4931,86 +5061,89 @@
       <c r="AG57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>316600</v>
+      </c>
+      <c r="E58" s="3">
         <v>319400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>516500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>514900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>517500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>19000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>68600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>21500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>20600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>70200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>120600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>18700</v>
-      </c>
-      <c r="O58" s="3">
-        <v>21600</v>
       </c>
       <c r="P58" s="3">
         <v>21600</v>
       </c>
       <c r="Q58" s="3">
+        <v>21600</v>
+      </c>
+      <c r="R58" s="3">
         <v>4600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>7700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>9100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>5500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>6900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>10900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>12900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>13200</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5026,86 +5159,89 @@
       <c r="AG58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>103300</v>
+      </c>
+      <c r="E59" s="3">
         <v>120600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>253200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>138800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>142800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>158600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>322900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>142200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>129000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>131100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>327500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>195500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>193400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>219100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>494400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>454100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>453300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>436200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>504800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>477300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>409400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>416200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>460000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>336200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>306100</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5121,86 +5257,89 @@
       <c r="AG59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1021800</v>
+      </c>
+      <c r="E60" s="3">
         <v>1031000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1288500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1290800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1311300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>843100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>909200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>818200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>766600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>865100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>955300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>867700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>846200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>883100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>929900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>875300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>850100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>848300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>933400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>872300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>778700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>798200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>838300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>705400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>607000</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5216,80 +5355,83 @@
       <c r="AG60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1614500</v>
+      </c>
+      <c r="E61" s="3">
         <v>1618700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1619000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1618700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1623800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2124900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2128600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2231000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2227300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2227400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2226100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2376400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2454200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2553700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2585700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2635900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2599200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2584500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2583800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2583100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1982500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1981800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1795300</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -5311,86 +5453,89 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>147600</v>
+      </c>
+      <c r="E62" s="3">
         <v>156400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>152300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>175500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>174600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>161700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>153900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>155200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>158300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>162800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>163400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>163600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>157200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>153700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>248200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>252500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>267200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>315400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>258900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>241600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>229200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>236100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>247700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>310900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>296000</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5406,8 +5551,11 @@
       <c r="AG62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5501,8 +5649,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5596,8 +5747,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5691,86 +5845,89 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2831500</v>
+      </c>
+      <c r="E66" s="3">
         <v>2865800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3117600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3140900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3167000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3187100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3250600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3263700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3211600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3313200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3398400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3456900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3504200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3638500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3766800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3766400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3719900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3751900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3779900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3701000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2994200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3019800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2885200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1020600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>907300</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5786,8 +5943,11 @@
       <c r="AG66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5821,8 +5981,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5916,8 +6077,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6011,8 +6175,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6106,8 +6273,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6201,86 +6371,89 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2045100</v>
+      </c>
+      <c r="E72" s="3">
         <v>2021300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1930500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1810600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1711500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1623300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1539100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1419300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1331300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1265000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1132100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1029800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>943100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>849700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>770800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>706900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>660800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>582900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>386700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>278600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>155500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>77400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-13600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1445800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1535400</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6296,8 +6469,11 @@
       <c r="AG72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6391,8 +6567,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6486,8 +6665,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6581,86 +6763,89 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1192700</v>
+      </c>
+      <c r="E76" s="3">
         <v>1258600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1244200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1232600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1201600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1095800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1051100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1034600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1016100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>984900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>890400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>759500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>696500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>636300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>576500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>497300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>499300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>548200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>569900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>470600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>345500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>264300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>187800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1583100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1658300</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6676,8 +6861,11 @@
       <c r="AG76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6771,203 +6959,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46206</v>
+      </c>
+      <c r="E80" s="2">
         <v>46115</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45835</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45744</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45562</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45471</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45380</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45198</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44743</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44652</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44470</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44379</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44288</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44099</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43917</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43735</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43644</v>
       </c>
-      <c r="AE80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AF80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AG80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E81" s="3">
         <v>94300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>123500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>102800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>91900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>87900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>123500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>91800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>70100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>136800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>106200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>90600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>97300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>82800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>67700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>50100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>33300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>250200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>112400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>127300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>82300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>91000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>136800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>141000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>68400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>121000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>189300</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7001,103 +7198,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>12900</v>
+        <v>12800</v>
       </c>
       <c r="E83" s="3">
         <v>12900</v>
       </c>
       <c r="F83" s="3">
+        <v>12900</v>
+      </c>
+      <c r="G83" s="3">
         <v>12000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>11100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>11400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>11100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>11000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>11300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>10400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>32100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>28700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>29000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>29100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>32100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>28700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>29000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>29100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>29300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>20000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>19200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>19800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>18700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>20700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>19600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>19300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>21200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>41300</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7191,8 +7392,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7286,8 +7490,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7381,8 +7588,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7476,8 +7686,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7571,103 +7784,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>116300</v>
+      </c>
+      <c r="E89" s="3">
         <v>46500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>190100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>110500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>100000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>110400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>168100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>121800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>46100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>91500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>164900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>131600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>77500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>81000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>181400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>91300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>7200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>41300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>139200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>125400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>53200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>163300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>210700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>245900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>179100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>55600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>148900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>173400</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7701,103 +7920,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-21400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-21700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-15300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-20200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-16700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-17700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-20100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-18600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-23800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-20200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-16600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-17400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-12400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-13700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-17000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-16500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-13600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-12900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-14900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-11200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-10700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-8400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-13300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-6500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-7500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-10600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-16400</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7891,8 +8114,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7986,103 +8212,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>54600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-21000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>30300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-27000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-17700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-16400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-18900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-27100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>51000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-16700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-17500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>94500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>9000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-105900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-16800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-203400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-18700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-959700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-13700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-15600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-13100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-6300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-16900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-14700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-16400</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8116,19 +8348,20 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E96" s="3">
         <v>3500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>3600</v>
-      </c>
-      <c r="F96" s="3">
-        <v>3700</v>
       </c>
       <c r="G96" s="3">
         <v>3700</v>
@@ -8140,19 +8373,19 @@
         <v>3700</v>
       </c>
       <c r="J96" s="3">
-        <v>3800</v>
+        <v>3700</v>
       </c>
       <c r="K96" s="3">
         <v>3800</v>
       </c>
       <c r="L96" s="3">
+        <v>3800</v>
+      </c>
+      <c r="M96" s="3">
         <v>3900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>3800</v>
-      </c>
-      <c r="N96" s="3">
-        <v>3900</v>
       </c>
       <c r="O96" s="3">
         <v>3900</v>
@@ -8161,10 +8394,10 @@
         <v>3900</v>
       </c>
       <c r="Q96" s="3">
+        <v>3900</v>
+      </c>
+      <c r="R96" s="3">
         <v>-3900</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-4000</v>
       </c>
       <c r="S96" s="3">
         <v>-4000</v>
@@ -8173,14 +8406,14 @@
         <v>-4000</v>
       </c>
       <c r="U96" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="V96" s="3">
         <v>-4300</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-4200</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
@@ -8211,8 +8444,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8306,8 +8542,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8401,8 +8640,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8496,270 +8738,279 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-137700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-281200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-128200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-68500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-54900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-119700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-115500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-109300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-93100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-74400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-74500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-90700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-135400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-87200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-99000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>13900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-263600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-5800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>593100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-7300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>145500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>163600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-237600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-175900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-34000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-129400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-157400</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E101" s="3">
         <v>4200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-10700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>6000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-3000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>3600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>4200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-5000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-8900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>4200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-5000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-8900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-3300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>11600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>4800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>3100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-4700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-4800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>400</v>
       </c>
-      <c r="AE101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AG101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-258400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>58400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>69600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>30600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-22800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>25500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-74700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>65100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>77300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>19600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>35800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>3700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>82800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-5700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-17700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-427500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>113700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-244500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>33100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>289800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>380500</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
-      </c>
       <c r="AA102" s="3">
         <v>0</v>
       </c>
@@ -8772,13 +9023,16 @@
       <c r="AD102" s="3">
         <v>0</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF102" s="3">
-        <v>0</v>
+      <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>0</v>
       </c>
     </row>
